--- a/doc/詳細設計/02_画面詳細設計/SCR-001_ログイン画面.xlsx
+++ b/doc/詳細設計/02_画面詳細設計/SCR-001_ログイン画面.xlsx
@@ -23,12 +23,101 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+  <si>
+    <t xml:space="preserve">項目</t>
+  </si>
+  <si>
+    <t xml:space="preserve">内容</t>
+  </si>
+  <si>
+    <t xml:space="preserve">画面ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCR001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">画面名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ログイン画面</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">権限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全ユーザー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">項目名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">種別</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必須</t>
+  </si>
+  <si>
+    <t xml:space="preserve">備考</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">テキスト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">○</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メール形式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスワード</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8文字以上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ボタン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">処理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ログイン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">認証API呼び出し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">条件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メッセージ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">認証失敗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDまたはパスワードが不正です</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -54,21 +143,42 @@
       <family val="0"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2A6099"/>
+        <bgColor rgb="FF666699"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -97,9 +207,29 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -111,7 +241,153 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF2A6099"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>159120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>51120</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>138600</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="813240" y="334440"/>
+          <a:ext cx="11430000" cy="6156720"/>
+          <a:chOff x="813240" y="334440"/>
+          <a:chExt cx="11430000" cy="6156720"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="1" name="画像 1" descr=""/>
+          <xdr:cNvPicPr/>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip r:embed="rId1"/>
+          <a:stretch/>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="813240" y="334440"/>
+            <a:ext cx="11430000" cy="6156720"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="0">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp>
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="2" name="シェイプ 1"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5421960" y="4902480"/>
+            <a:ext cx="2077560" cy="331560"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="ffffff"/>
+          </a:solidFill>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="ffffff"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0"/>
+          <a:fillRef idx="0"/>
+          <a:effectRef idx="0"/>
+          <a:fontRef idx="minor"/>
+        </xdr:style>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -291,9 +567,54 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="B1:C7"/>
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.57"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -311,7 +632,72 @@
   </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;Kffffffページ &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B1:E5"/>
+  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -322,14 +708,35 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="B1:C4"/>
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.86"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -340,32 +747,42 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;Kffffffページ &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="B1:C4"/>
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.59"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:C2"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/doc/詳細設計/02_画面詳細設計/SCR-001_ログイン画面.xlsx
+++ b/doc/詳細設計/02_画面詳細設計/SCR-001_ログイン画面.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="基本情報" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="96">
   <si>
     <t xml:space="preserve">項目</t>
   </si>
@@ -56,6 +56,12 @@
     <t xml:space="preserve">全ユーザー</t>
   </si>
   <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">項目ID</t>
+  </si>
+  <si>
     <t xml:space="preserve">項目名</t>
   </si>
   <si>
@@ -65,49 +71,247 @@
     <t xml:space="preserve">必須</t>
   </si>
   <si>
-    <t xml:space="preserve">備考</t>
-  </si>
-  <si>
-    <t xml:space="preserve">メール</t>
-  </si>
-  <si>
-    <t xml:space="preserve">テキスト</t>
+    <t xml:space="preserve">桁数/形式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">説明</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メールアドレス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">テキストボックス</t>
   </si>
   <si>
     <t xml:space="preserve">○</t>
   </si>
   <si>
-    <t xml:space="preserve">メール形式</t>
+    <t xml:space="preserve">255文字以内 / Email形式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ログインに使用するメールアドレスを入力する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">password</t>
   </si>
   <si>
     <t xml:space="preserve">パスワード</t>
   </si>
   <si>
-    <t xml:space="preserve">8文字以上</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ボタン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">処理</t>
+    <t xml:space="preserve">パスワード入力</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8～100文字</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ログインに使用するパスワードを入力する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passwordVisibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスワード表示切替</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アイコン（ボタン）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスワードの表示/非表示を切り替える</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adminCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">管理者コード（任意）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">任意</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最大50文字</t>
+  </si>
+  <si>
+    <t xml:space="preserve">管理者ユーザー用コードを入力する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forgotPasswordLink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスワードをお忘れですか？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">リンク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスワード再設定画面へ遷移する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">勤怠管理システム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ラベル（見出し）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">システムタイトルを表示する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subtitle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ログインして勤怠を記録しましょう</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ラベル（サブタイトル）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">サブタイトルを表示する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">copyright</t>
+  </si>
+  <si>
+    <t xml:space="preserve">© 2026 勤怠管理システム. All rights reserved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ラベル（フッター）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">著作権表示を行う</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ボタンID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ボタン名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">配置場所</t>
+  </si>
+  <si>
+    <t xml:space="preserve">処理内容</t>
+  </si>
+  <si>
+    <t xml:space="preserve">btnLogin</t>
   </si>
   <si>
     <t xml:space="preserve">ログイン</t>
   </si>
   <si>
-    <t xml:space="preserve">認証API呼び出し</t>
-  </si>
-  <si>
-    <t xml:space="preserve">条件</t>
-  </si>
-  <si>
-    <t xml:space="preserve">メッセージ</t>
+    <t xml:space="preserve">プライマリボタン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フォーム下部</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入力内容を検証し、ログイン認証を実施する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">btnPasswordToggle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アイコンボタン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスワード入力欄右側</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lnkForgotPassword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">テキストリンク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ログインボタン下部</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メッセージID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">対象項目</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エラーメッセージ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">発生条件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-LOGIN-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メールアドレスを入力してください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メールアドレス未入力</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-LOGIN-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メールアドレスの形式が不正です。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email形式不正</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-LOGIN-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスワードを入力してください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスワード未入力</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-LOGIN-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ログイン認証</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メールアドレスまたはパスワードが正しくありません。</t>
   </si>
   <si>
     <t xml:space="preserve">認証失敗</t>
   </si>
   <si>
-    <t xml:space="preserve">IDまたはパスワードが不正です</t>
+    <t xml:space="preserve">E-LOGIN-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アカウントがロックされています。管理者へ連絡してください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ログイン失敗回数超過</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-LOGIN-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">システム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">システムエラーが発生しました。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API異常</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-LOGIN-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">サーバーとの通信に失敗しました。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通信エラー</t>
   </si>
 </sst>
 </file>
@@ -207,7 +411,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -225,6 +429,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -309,82 +517,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>360</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>159120</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>51120</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>138600</xdr:rowOff>
+      <xdr:colOff>560880</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>31680</xdr:rowOff>
     </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="0" name=""/>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="画像 1" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="813240" y="334440"/>
-          <a:ext cx="11430000" cy="6156720"/>
-          <a:chOff x="813240" y="334440"/>
-          <a:chExt cx="11430000" cy="6156720"/>
+          <a:off x="812880" y="337680"/>
+          <a:ext cx="11940120" cy="6209280"/>
         </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="1" name="画像 1" descr=""/>
-          <xdr:cNvPicPr/>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip r:embed="rId1"/>
-          <a:stretch/>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="813240" y="334440"/>
-            <a:ext cx="11430000" cy="6156720"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
-          <a:ln w="0">
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp>
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="2" name="シェイプ 1"/>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5421960" y="4902480"/>
-            <a:ext cx="2077560" cy="331560"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="ffffff"/>
-          </a:solidFill>
-          <a:ln w="0">
-            <a:solidFill>
-              <a:srgbClr val="ffffff"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="0"/>
-          <a:fillRef idx="0"/>
-          <a:effectRef idx="0"/>
-          <a:fontRef idx="minor"/>
-        </xdr:style>
-      </xdr:sp>
-    </xdr:grpSp>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -651,10 +816,28 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:E5"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.92"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="43.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.06"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="21.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="46.76"/>
+  </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
         <v>10</v>
@@ -668,34 +851,271 @@
       <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
-        <v>14</v>
+      <c r="B4" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
-        <v>18</v>
+      <c r="B5" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>19</v>
       </c>
+      <c r="F7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -713,27 +1133,96 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:C4"/>
+  <dimension ref="B1:G6"/>
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="23.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="43.01"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>54</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
-        <v>22</v>
+      <c r="B4" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>23</v>
+        <v>58</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -752,31 +1241,154 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:C4"/>
+  <dimension ref="B1:F10"/>
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="55.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="25.99"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>27</v>
+      <c r="E6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/doc/詳細設計/02_画面詳細設計/SCR-001_ログイン画面.xlsx
+++ b/doc/詳細設計/02_画面詳細設計/SCR-001_ログイン画面.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="基本情報" sheetId="1" state="visible" r:id="rId3"/>
@@ -523,9 +523,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>560880</xdr:colOff>
+      <xdr:colOff>560520</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>31680</xdr:rowOff>
+      <xdr:rowOff>31320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -539,7 +539,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="812880" y="337680"/>
-          <a:ext cx="11940120" cy="6209280"/>
+          <a:ext cx="11939760" cy="6208920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
